--- a/Ashish_Excel_Sales_Dashboard.xlsx
+++ b/Ashish_Excel_Sales_Dashboard.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +33,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="20"/>
     </font>
     <font>
       <i val="1"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,15 +58,20 @@
       <sz val="18"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,31 +79,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E1F2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -284,109 +300,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Region Revenue</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!E10</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$D$11:$D$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$E$11:$E$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Revenue (₹)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -411,28 +324,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4680000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -448,7 +339,7 @@
     <tableColumn id="6" name="Unit Price"/>
     <tableColumn id="7" name="Revenue"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
 </table>
 </file>
 
@@ -754,37 +645,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
@@ -794,8 +685,8 @@
       <c r="A2" t="n">
         <v>1001</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>45678</v>
+      <c r="B2" s="2" t="n">
+        <v>45658</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,16 +695,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G2" s="2">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G2" s="3">
         <f>E2*F2</f>
         <v/>
       </c>
@@ -822,8 +713,8 @@
       <c r="A3" t="n">
         <v>1002</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>45665</v>
+      <c r="B3" s="2" t="n">
+        <v>45662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,12 +727,12 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <f>E3*F3</f>
         <v/>
       </c>
@@ -850,12 +741,12 @@
       <c r="A4" t="n">
         <v>1003</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>45679</v>
+      <c r="B4" s="2" t="n">
+        <v>45660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -866,10 +757,10 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <f>E4*F4</f>
         <v/>
       </c>
@@ -878,26 +769,26 @@
       <c r="A5" t="n">
         <v>1004</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>45676</v>
+      <c r="B5" s="2" t="n">
+        <v>45660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="F5" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G5" s="3">
         <f>E5*F5</f>
         <v/>
       </c>
@@ -906,8 +797,8 @@
       <c r="A6" t="n">
         <v>1005</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>45660</v>
+      <c r="B6" s="2" t="n">
+        <v>45677</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -920,12 +811,12 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <f>E6*F6</f>
         <v/>
       </c>
@@ -934,8 +825,8 @@
       <c r="A7" t="n">
         <v>1006</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>45675</v>
+      <c r="B7" s="2" t="n">
+        <v>45680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -944,16 +835,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G7" s="3">
         <f>E7*F7</f>
         <v/>
       </c>
@@ -962,8 +853,8 @@
       <c r="A8" t="n">
         <v>1007</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>45665</v>
+      <c r="B8" s="2" t="n">
+        <v>45676</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -972,16 +863,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G8" s="2">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G8" s="3">
         <f>E8*F8</f>
         <v/>
       </c>
@@ -990,8 +881,8 @@
       <c r="A9" t="n">
         <v>1008</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>45683</v>
+      <c r="B9" s="2" t="n">
+        <v>45680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1006,10 +897,10 @@
       <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <f>E9*F9</f>
         <v/>
       </c>
@@ -1018,8 +909,8 @@
       <c r="A10" t="n">
         <v>1009</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>45668</v>
+      <c r="B10" s="2" t="n">
+        <v>45662</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1032,12 +923,12 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <f>E10*F10</f>
         <v/>
       </c>
@@ -1046,12 +937,12 @@
       <c r="A11" t="n">
         <v>1010</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>45682</v>
+      <c r="B11" s="2" t="n">
+        <v>45660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1062,10 +953,10 @@
       <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <f>E11*F11</f>
         <v/>
       </c>
@@ -1074,8 +965,8 @@
       <c r="A12" t="n">
         <v>1011</v>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>45701</v>
+      <c r="B12" s="2" t="n">
+        <v>45716</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1090,10 +981,10 @@
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <f>E12*F12</f>
         <v/>
       </c>
@@ -1102,26 +993,26 @@
       <c r="A13" t="n">
         <v>1012</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>45708</v>
+      <c r="B13" s="2" t="n">
+        <v>45714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G13" s="2">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G13" s="3">
         <f>E13*F13</f>
         <v/>
       </c>
@@ -1130,7 +1021,7 @@
       <c r="A14" t="n">
         <v>1013</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1140,16 +1031,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G14" s="2">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G14" s="3">
         <f>E14*F14</f>
         <v/>
       </c>
@@ -1158,7 +1049,7 @@
       <c r="A15" t="n">
         <v>1014</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1168,16 +1059,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G15" s="3">
         <f>E15*F15</f>
         <v/>
       </c>
@@ -1186,26 +1077,26 @@
       <c r="A16" t="n">
         <v>1015</v>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>45707</v>
+      <c r="B16" s="2" t="n">
+        <v>45716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G16" s="2">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G16" s="3">
         <f>E16*F16</f>
         <v/>
       </c>
@@ -1214,8 +1105,8 @@
       <c r="A17" t="n">
         <v>1016</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>45710</v>
+      <c r="B17" s="2" t="n">
+        <v>45711</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1224,16 +1115,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G17" s="3">
         <f>E17*F17</f>
         <v/>
       </c>
@@ -1242,26 +1133,26 @@
       <c r="A18" t="n">
         <v>1017</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>45716</v>
+      <c r="B18" s="2" t="n">
+        <v>45696</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G18" s="2">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G18" s="3">
         <f>E18*F18</f>
         <v/>
       </c>
@@ -1270,26 +1161,26 @@
       <c r="A19" t="n">
         <v>1018</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>45697</v>
+      <c r="B19" s="2" t="n">
+        <v>45716</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G19" s="2">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G19" s="3">
         <f>E19*F19</f>
         <v/>
       </c>
@@ -1298,26 +1189,26 @@
       <c r="A20" t="n">
         <v>1019</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>45694</v>
+      <c r="B20" s="2" t="n">
+        <v>45703</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G20" s="2">
+        <v>6</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G20" s="3">
         <f>E20*F20</f>
         <v/>
       </c>
@@ -1326,26 +1217,26 @@
       <c r="A21" t="n">
         <v>1020</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>45710</v>
+      <c r="B21" s="2" t="n">
+        <v>45700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G21" s="2">
+        <v>7</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G21" s="3">
         <f>E21*F21</f>
         <v/>
       </c>
@@ -1354,12 +1245,12 @@
       <c r="A22" t="n">
         <v>1021</v>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>45736</v>
+      <c r="B22" s="2" t="n">
+        <v>45739</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1368,12 +1259,12 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <f>E22*F22</f>
         <v/>
       </c>
@@ -1382,26 +1273,26 @@
       <c r="A23" t="n">
         <v>1022</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G23" s="2">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G23" s="3">
         <f>E23*F23</f>
         <v/>
       </c>
@@ -1410,26 +1301,26 @@
       <c r="A24" t="n">
         <v>1023</v>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>45737</v>
+      <c r="B24" s="2" t="n">
+        <v>45729</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G24" s="2">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G24" s="3">
         <f>E24*F24</f>
         <v/>
       </c>
@@ -1438,26 +1329,26 @@
       <c r="A25" t="n">
         <v>1024</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>45738</v>
+      <c r="B25" s="2" t="n">
+        <v>45724</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G25" s="2">
+        <v>10</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G25" s="3">
         <f>E25*F25</f>
         <v/>
       </c>
@@ -1466,12 +1357,12 @@
       <c r="A26" t="n">
         <v>1025</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45743</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1480,12 +1371,12 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <f>E26*F26</f>
         <v/>
       </c>
@@ -1494,26 +1385,26 @@
       <c r="A27" t="n">
         <v>1026</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G27" s="2">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G27" s="3">
         <f>E27*F27</f>
         <v/>
       </c>
@@ -1522,26 +1413,26 @@
       <c r="A28" t="n">
         <v>1027</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>45723</v>
+      <c r="B28" s="2" t="n">
+        <v>45739</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G28" s="2">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G28" s="3">
         <f>E28*F28</f>
         <v/>
       </c>
@@ -1550,26 +1441,26 @@
       <c r="A29" t="n">
         <v>1028</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>45737</v>
+      <c r="B29" s="2" t="n">
+        <v>45732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G29" s="2">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G29" s="3">
         <f>E29*F29</f>
         <v/>
       </c>
@@ -1578,7 +1469,7 @@
       <c r="A30" t="n">
         <v>1029</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1588,16 +1479,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G30" s="2">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G30" s="3">
         <f>E30*F30</f>
         <v/>
       </c>
@@ -1606,26 +1497,26 @@
       <c r="A31" t="n">
         <v>1030</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G31" s="2">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G31" s="3">
         <f>E31*F31</f>
         <v/>
       </c>
@@ -1634,8 +1525,8 @@
       <c r="A32" t="n">
         <v>1031</v>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>45759</v>
+      <c r="B32" s="2" t="n">
+        <v>45761</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1644,16 +1535,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G32" s="2">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G32" s="3">
         <f>E32*F32</f>
         <v/>
       </c>
@@ -1662,26 +1553,26 @@
       <c r="A33" t="n">
         <v>1032</v>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>45750</v>
+      <c r="B33" s="2" t="n">
+        <v>45752</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G33" s="2">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G33" s="3">
         <f>E33*F33</f>
         <v/>
       </c>
@@ -1690,26 +1581,26 @@
       <c r="A34" t="n">
         <v>1033</v>
       </c>
-      <c r="B34" s="1" t="n">
-        <v>45768</v>
+      <c r="B34" s="2" t="n">
+        <v>45775</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G34" s="2">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G34" s="3">
         <f>E34*F34</f>
         <v/>
       </c>
@@ -1718,8 +1609,8 @@
       <c r="A35" t="n">
         <v>1034</v>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>45767</v>
+      <c r="B35" s="2" t="n">
+        <v>45753</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1728,16 +1619,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G35" s="2">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G35" s="3">
         <f>E35*F35</f>
         <v/>
       </c>
@@ -1746,26 +1637,26 @@
       <c r="A36" t="n">
         <v>1035</v>
       </c>
-      <c r="B36" s="1" t="n">
-        <v>45767</v>
+      <c r="B36" s="2" t="n">
+        <v>45760</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G36" s="2">
+        <v>3</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G36" s="3">
         <f>E36*F36</f>
         <v/>
       </c>
@@ -1774,26 +1665,26 @@
       <c r="A37" t="n">
         <v>1036</v>
       </c>
-      <c r="B37" s="1" t="n">
-        <v>45765</v>
+      <c r="B37" s="2" t="n">
+        <v>45764</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G37" s="2">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G37" s="3">
         <f>E37*F37</f>
         <v/>
       </c>
@@ -1802,12 +1693,12 @@
       <c r="A38" t="n">
         <v>1037</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1816,12 +1707,12 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
-      </c>
-      <c r="F38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="3">
         <f>E38*F38</f>
         <v/>
       </c>
@@ -1830,26 +1721,26 @@
       <c r="A39" t="n">
         <v>1038</v>
       </c>
-      <c r="B39" s="1" t="n">
-        <v>45751</v>
+      <c r="B39" s="2" t="n">
+        <v>45772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G39" s="2">
+        <v>10</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G39" s="3">
         <f>E39*F39</f>
         <v/>
       </c>
@@ -1858,26 +1749,26 @@
       <c r="A40" t="n">
         <v>1039</v>
       </c>
-      <c r="B40" s="1" t="n">
-        <v>45762</v>
+      <c r="B40" s="2" t="n">
+        <v>45751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G40" s="2">
+        <v>7</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G40" s="3">
         <f>E40*F40</f>
         <v/>
       </c>
@@ -1886,26 +1777,26 @@
       <c r="A41" t="n">
         <v>1040</v>
       </c>
-      <c r="B41" s="1" t="n">
-        <v>45764</v>
+      <c r="B41" s="2" t="n">
+        <v>45762</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G41" s="2">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G41" s="3">
         <f>E41*F41</f>
         <v/>
       </c>
@@ -1914,8 +1805,8 @@
       <c r="A42" t="n">
         <v>1041</v>
       </c>
-      <c r="B42" s="1" t="n">
-        <v>45804</v>
+      <c r="B42" s="2" t="n">
+        <v>45794</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1928,12 +1819,12 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="3">
         <f>E42*F42</f>
         <v/>
       </c>
@@ -1942,26 +1833,26 @@
       <c r="A43" t="n">
         <v>1042</v>
       </c>
-      <c r="B43" s="1" t="n">
-        <v>45782</v>
+      <c r="B43" s="2" t="n">
+        <v>45805</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G43" s="2">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G43" s="3">
         <f>E43*F43</f>
         <v/>
       </c>
@@ -1970,26 +1861,26 @@
       <c r="A44" t="n">
         <v>1043</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G44" s="2">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G44" s="3">
         <f>E44*F44</f>
         <v/>
       </c>
@@ -1998,8 +1889,8 @@
       <c r="A45" t="n">
         <v>1044</v>
       </c>
-      <c r="B45" s="1" t="n">
-        <v>45781</v>
+      <c r="B45" s="2" t="n">
+        <v>45802</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2008,16 +1899,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G45" s="2">
+        <v>7</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G45" s="3">
         <f>E45*F45</f>
         <v/>
       </c>
@@ -2026,26 +1917,26 @@
       <c r="A46" t="n">
         <v>1045</v>
       </c>
-      <c r="B46" s="1" t="n">
-        <v>45779</v>
+      <c r="B46" s="2" t="n">
+        <v>45778</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G46" s="2">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G46" s="3">
         <f>E46*F46</f>
         <v/>
       </c>
@@ -2054,26 +1945,26 @@
       <c r="A47" t="n">
         <v>1046</v>
       </c>
-      <c r="B47" s="1" t="n">
-        <v>45780</v>
+      <c r="B47" s="2" t="n">
+        <v>45781</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G47" s="3">
         <f>E47*F47</f>
         <v/>
       </c>
@@ -2082,8 +1973,8 @@
       <c r="A48" t="n">
         <v>1047</v>
       </c>
-      <c r="B48" s="1" t="n">
-        <v>45802</v>
+      <c r="B48" s="2" t="n">
+        <v>45779</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2092,16 +1983,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G48" s="2">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G48" s="3">
         <f>E48*F48</f>
         <v/>
       </c>
@@ -2110,26 +2001,26 @@
       <c r="A49" t="n">
         <v>1048</v>
       </c>
-      <c r="B49" s="1" t="n">
-        <v>45799</v>
+      <c r="B49" s="2" t="n">
+        <v>45780</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G49" s="2">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G49" s="3">
         <f>E49*F49</f>
         <v/>
       </c>
@@ -2138,26 +2029,26 @@
       <c r="A50" t="n">
         <v>1049</v>
       </c>
-      <c r="B50" s="1" t="n">
-        <v>45786</v>
+      <c r="B50" s="2" t="n">
+        <v>45802</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G50" s="2">
+        <v>10</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G50" s="3">
         <f>E50*F50</f>
         <v/>
       </c>
@@ -2166,26 +2057,26 @@
       <c r="A51" t="n">
         <v>1050</v>
       </c>
-      <c r="B51" s="1" t="n">
-        <v>45784</v>
+      <c r="B51" s="2" t="n">
+        <v>45793</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G51" s="2">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G51" s="3">
         <f>E51*F51</f>
         <v/>
       </c>
@@ -2194,26 +2085,26 @@
       <c r="A52" t="n">
         <v>1051</v>
       </c>
-      <c r="B52" s="1" t="n">
-        <v>45821</v>
+      <c r="B52" s="2" t="n">
+        <v>45836</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G52" s="2">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
         <f>E52*F52</f>
         <v/>
       </c>
@@ -2222,26 +2113,26 @@
       <c r="A53" t="n">
         <v>1052</v>
       </c>
-      <c r="B53" s="1" t="n">
-        <v>45823</v>
+      <c r="B53" s="2" t="n">
+        <v>45833</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G53" s="2">
+        <v>10</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G53" s="3">
         <f>E53*F53</f>
         <v/>
       </c>
@@ -2250,8 +2141,8 @@
       <c r="A54" t="n">
         <v>1053</v>
       </c>
-      <c r="B54" s="1" t="n">
-        <v>45816</v>
+      <c r="B54" s="2" t="n">
+        <v>45821</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2260,16 +2151,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G54" s="2">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G54" s="3">
         <f>E54*F54</f>
         <v/>
       </c>
@@ -2278,26 +2169,26 @@
       <c r="A55" t="n">
         <v>1054</v>
       </c>
-      <c r="B55" s="1" t="n">
-        <v>45809</v>
+      <c r="B55" s="2" t="n">
+        <v>45823</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>10</v>
       </c>
-      <c r="F55" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G55" s="2">
+      <c r="F55" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G55" s="3">
         <f>E55*F55</f>
         <v/>
       </c>
@@ -2306,12 +2197,12 @@
       <c r="A56" t="n">
         <v>1055</v>
       </c>
-      <c r="B56" s="1" t="n">
-        <v>45827</v>
+      <c r="B56" s="2" t="n">
+        <v>45811</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2320,12 +2211,12 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="3">
         <f>E56*F56</f>
         <v/>
       </c>
@@ -2334,8 +2225,8 @@
       <c r="A57" t="n">
         <v>1056</v>
       </c>
-      <c r="B57" s="1" t="n">
-        <v>45831</v>
+      <c r="B57" s="2" t="n">
+        <v>45826</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2344,16 +2235,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G57" s="2">
+        <v>11</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G57" s="3">
         <f>E57*F57</f>
         <v/>
       </c>
@@ -2362,8 +2253,8 @@
       <c r="A58" t="n">
         <v>1057</v>
       </c>
-      <c r="B58" s="1" t="n">
-        <v>45811</v>
+      <c r="B58" s="2" t="n">
+        <v>45809</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2372,16 +2263,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G58" s="2">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G58" s="3">
         <f>E58*F58</f>
         <v/>
       </c>
@@ -2390,26 +2281,26 @@
       <c r="A59" t="n">
         <v>1058</v>
       </c>
-      <c r="B59" s="1" t="n">
-        <v>45825</v>
+      <c r="B59" s="2" t="n">
+        <v>45810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G59" s="2">
+        <v>12</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G59" s="3">
         <f>E59*F59</f>
         <v/>
       </c>
@@ -2418,26 +2309,26 @@
       <c r="A60" t="n">
         <v>1059</v>
       </c>
-      <c r="B60" s="1" t="n">
-        <v>45815</v>
+      <c r="B60" s="2" t="n">
+        <v>45836</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G60" s="2">
+        <v>2</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G60" s="3">
         <f>E60*F60</f>
         <v/>
       </c>
@@ -2446,26 +2337,26 @@
       <c r="A61" t="n">
         <v>1060</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45816</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G61" s="2">
+        <v>10</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G61" s="3">
         <f>E61*F61</f>
         <v/>
       </c>
@@ -2474,26 +2365,26 @@
       <c r="A62" t="n">
         <v>1061</v>
       </c>
-      <c r="B62" s="1" t="n">
-        <v>45842</v>
+      <c r="B62" s="2" t="n">
+        <v>45845</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G62" s="2">
+        <v>9</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G62" s="3">
         <f>E62*F62</f>
         <v/>
       </c>
@@ -2502,8 +2393,8 @@
       <c r="A63" t="n">
         <v>1062</v>
       </c>
-      <c r="B63" s="1" t="n">
-        <v>45850</v>
+      <c r="B63" s="2" t="n">
+        <v>45857</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2512,16 +2403,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G63" s="2">
+        <v>11</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G63" s="3">
         <f>E63*F63</f>
         <v/>
       </c>
@@ -2530,26 +2421,26 @@
       <c r="A64" t="n">
         <v>1063</v>
       </c>
-      <c r="B64" s="1" t="n">
-        <v>45866</v>
+      <c r="B64" s="2" t="n">
+        <v>45864</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G64" s="2">
+        <v>9</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G64" s="3">
         <f>E64*F64</f>
         <v/>
       </c>
@@ -2558,26 +2449,26 @@
       <c r="A65" t="n">
         <v>1064</v>
       </c>
-      <c r="B65" s="1" t="n">
-        <v>45840</v>
+      <c r="B65" s="2" t="n">
+        <v>45842</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G65" s="2">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G65" s="3">
         <f>E65*F65</f>
         <v/>
       </c>
@@ -2586,8 +2477,8 @@
       <c r="A66" t="n">
         <v>1065</v>
       </c>
-      <c r="B66" s="1" t="n">
-        <v>45846</v>
+      <c r="B66" s="2" t="n">
+        <v>45852</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2596,16 +2487,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G66" s="2">
+        <v>8</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G66" s="3">
         <f>E66*F66</f>
         <v/>
       </c>
@@ -2614,26 +2505,26 @@
       <c r="A67" t="n">
         <v>1066</v>
       </c>
-      <c r="B67" s="1" t="n">
-        <v>45843</v>
+      <c r="B67" s="2" t="n">
+        <v>45860</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G67" s="2">
+        <v>2</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G67" s="3">
         <f>E67*F67</f>
         <v/>
       </c>
@@ -2642,26 +2533,26 @@
       <c r="A68" t="n">
         <v>1067</v>
       </c>
-      <c r="B68" s="1" t="n">
-        <v>45853</v>
+      <c r="B68" s="2" t="n">
+        <v>45862</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G68" s="2">
+        <v>8</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G68" s="3">
         <f>E68*F68</f>
         <v/>
       </c>
@@ -2670,26 +2561,26 @@
       <c r="A69" t="n">
         <v>1068</v>
       </c>
-      <c r="B69" s="1" t="n">
-        <v>45864</v>
+      <c r="B69" s="2" t="n">
+        <v>45845</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G69" s="2">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G69" s="3">
         <f>E69*F69</f>
         <v/>
       </c>
@@ -2698,12 +2589,12 @@
       <c r="A70" t="n">
         <v>1069</v>
       </c>
-      <c r="B70" s="1" t="n">
-        <v>45859</v>
+      <c r="B70" s="2" t="n">
+        <v>45843</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2712,12 +2603,12 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="3">
         <f>E70*F70</f>
         <v/>
       </c>
@@ -2726,12 +2617,12 @@
       <c r="A71" t="n">
         <v>1070</v>
       </c>
-      <c r="B71" s="1" t="n">
-        <v>45863</v>
+      <c r="B71" s="2" t="n">
+        <v>45853</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2740,12 +2631,12 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="3">
         <f>E71*F71</f>
         <v/>
       </c>
@@ -2754,26 +2645,26 @@
       <c r="A72" t="n">
         <v>1071</v>
       </c>
-      <c r="B72" s="1" t="n">
-        <v>45885</v>
+      <c r="B72" s="2" t="n">
+        <v>45895</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G72" s="2">
+        <v>9</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G72" s="3">
         <f>E72*F72</f>
         <v/>
       </c>
@@ -2782,8 +2673,8 @@
       <c r="A73" t="n">
         <v>1072</v>
       </c>
-      <c r="B73" s="1" t="n">
-        <v>45871</v>
+      <c r="B73" s="2" t="n">
+        <v>45887</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2792,16 +2683,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G73" s="2">
+        <v>12</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G73" s="3">
         <f>E73*F73</f>
         <v/>
       </c>
@@ -2810,26 +2701,26 @@
       <c r="A74" t="n">
         <v>1073</v>
       </c>
-      <c r="B74" s="1" t="n">
-        <v>45882</v>
+      <c r="B74" s="2" t="n">
+        <v>45875</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G74" s="2">
+        <v>5</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G74" s="3">
         <f>E74*F74</f>
         <v/>
       </c>
@@ -2838,8 +2729,8 @@
       <c r="A75" t="n">
         <v>1074</v>
       </c>
-      <c r="B75" s="1" t="n">
-        <v>45883</v>
+      <c r="B75" s="2" t="n">
+        <v>45876</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2848,16 +2739,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G75" s="2">
+        <v>9</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G75" s="3">
         <f>E75*F75</f>
         <v/>
       </c>
@@ -2866,26 +2757,26 @@
       <c r="A76" t="n">
         <v>1075</v>
       </c>
-      <c r="B76" s="1" t="n">
-        <v>45874</v>
+      <c r="B76" s="2" t="n">
+        <v>45882</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G76" s="2">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G76" s="3">
         <f>E76*F76</f>
         <v/>
       </c>
@@ -2894,26 +2785,26 @@
       <c r="A77" t="n">
         <v>1076</v>
       </c>
-      <c r="B77" s="1" t="n">
-        <v>45871</v>
+      <c r="B77" s="2" t="n">
+        <v>45895</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G77" s="2">
+        <v>6</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G77" s="3">
         <f>E77*F77</f>
         <v/>
       </c>
@@ -2922,12 +2813,12 @@
       <c r="A78" t="n">
         <v>1077</v>
       </c>
-      <c r="B78" s="1" t="n">
-        <v>45893</v>
+      <c r="B78" s="2" t="n">
+        <v>45892</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2936,12 +2827,12 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78" s="3">
         <f>E78*F78</f>
         <v/>
       </c>
@@ -2950,8 +2841,8 @@
       <c r="A79" t="n">
         <v>1078</v>
       </c>
-      <c r="B79" s="1" t="n">
-        <v>45888</v>
+      <c r="B79" s="2" t="n">
+        <v>45879</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2960,16 +2851,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G79" s="2">
+        <v>5</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G79" s="3">
         <f>E79*F79</f>
         <v/>
       </c>
@@ -2978,26 +2869,26 @@
       <c r="A80" t="n">
         <v>1079</v>
       </c>
-      <c r="B80" s="1" t="n">
-        <v>45871</v>
+      <c r="B80" s="2" t="n">
+        <v>45893</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G80" s="2">
+        <v>11</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G80" s="3">
         <f>E80*F80</f>
         <v/>
       </c>
@@ -3006,26 +2897,26 @@
       <c r="A81" t="n">
         <v>1080</v>
       </c>
-      <c r="B81" s="1" t="n">
-        <v>45872</v>
+      <c r="B81" s="2" t="n">
+        <v>45871</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G81" s="2">
+        <v>7</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G81" s="3">
         <f>E81*F81</f>
         <v/>
       </c>
@@ -3034,8 +2925,8 @@
       <c r="A82" t="n">
         <v>1081</v>
       </c>
-      <c r="B82" s="1" t="n">
-        <v>45913</v>
+      <c r="B82" s="2" t="n">
+        <v>45917</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3044,16 +2935,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G82" s="2">
+        <v>9</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G82" s="3">
         <f>E82*F82</f>
         <v/>
       </c>
@@ -3062,26 +2953,26 @@
       <c r="A83" t="n">
         <v>1082</v>
       </c>
-      <c r="B83" s="1" t="n">
-        <v>45919</v>
+      <c r="B83" s="2" t="n">
+        <v>45903</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G83" s="2">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G83" s="3">
         <f>E83*F83</f>
         <v/>
       </c>
@@ -3090,26 +2981,26 @@
       <c r="A84" t="n">
         <v>1083</v>
       </c>
-      <c r="B84" s="1" t="n">
-        <v>45914</v>
+      <c r="B84" s="2" t="n">
+        <v>45903</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>11</v>
       </c>
-      <c r="F84" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G84" s="2">
+      <c r="F84" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G84" s="3">
         <f>E84*F84</f>
         <v/>
       </c>
@@ -3118,26 +3009,26 @@
       <c r="A85" t="n">
         <v>1084</v>
       </c>
-      <c r="B85" s="1" t="n">
-        <v>45909</v>
+      <c r="B85" s="2" t="n">
+        <v>45919</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G85" s="2">
+        <v>3</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G85" s="3">
         <f>E85*F85</f>
         <v/>
       </c>
@@ -3146,26 +3037,26 @@
       <c r="A86" t="n">
         <v>1085</v>
       </c>
-      <c r="B86" s="1" t="n">
-        <v>45908</v>
+      <c r="B86" s="2" t="n">
+        <v>45902</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G86" s="2">
+        <v>11</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G86" s="3">
         <f>E86*F86</f>
         <v/>
       </c>
@@ -3174,26 +3065,26 @@
       <c r="A87" t="n">
         <v>1086</v>
       </c>
-      <c r="B87" s="1" t="n">
-        <v>45922</v>
+      <c r="B87" s="2" t="n">
+        <v>45919</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G87" s="2">
+        <v>12</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G87" s="3">
         <f>E87*F87</f>
         <v/>
       </c>
@@ -3202,26 +3093,26 @@
       <c r="A88" t="n">
         <v>1087</v>
       </c>
-      <c r="B88" s="1" t="n">
-        <v>45911</v>
+      <c r="B88" s="2" t="n">
+        <v>45922</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G88" s="2">
+        <v>5</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G88" s="3">
         <f>E88*F88</f>
         <v/>
       </c>
@@ -3230,26 +3121,26 @@
       <c r="A89" t="n">
         <v>1088</v>
       </c>
-      <c r="B89" s="1" t="n">
-        <v>45920</v>
+      <c r="B89" s="2" t="n">
+        <v>45913</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G89" s="2">
+        <v>6</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G89" s="3">
         <f>E89*F89</f>
         <v/>
       </c>
@@ -3258,26 +3149,26 @@
       <c r="A90" t="n">
         <v>1089</v>
       </c>
-      <c r="B90" s="1" t="n">
-        <v>45918</v>
+      <c r="B90" s="2" t="n">
+        <v>45910</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G90" s="2">
+        <v>12</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G90" s="3">
         <f>E90*F90</f>
         <v/>
       </c>
@@ -3286,12 +3177,12 @@
       <c r="A91" t="n">
         <v>1090</v>
       </c>
-      <c r="B91" s="1" t="n">
-        <v>45905</v>
+      <c r="B91" s="2" t="n">
+        <v>45901</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3302,10 +3193,10 @@
       <c r="E91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="3">
         <f>E91*F91</f>
         <v/>
       </c>
@@ -3314,26 +3205,26 @@
       <c r="A92" t="n">
         <v>1091</v>
       </c>
-      <c r="B92" s="1" t="n">
-        <v>45942</v>
+      <c r="B92" s="2" t="n">
+        <v>45934</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G92" s="2">
+        <v>11</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G92" s="3">
         <f>E92*F92</f>
         <v/>
       </c>
@@ -3342,12 +3233,12 @@
       <c r="A93" t="n">
         <v>1092</v>
       </c>
-      <c r="B93" s="1" t="n">
-        <v>45957</v>
+      <c r="B93" s="2" t="n">
+        <v>45947</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3356,12 +3247,12 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
-      </c>
-      <c r="F93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="G93" s="2">
+      <c r="G93" s="3">
         <f>E93*F93</f>
         <v/>
       </c>
@@ -3370,26 +3261,26 @@
       <c r="A94" t="n">
         <v>1093</v>
       </c>
-      <c r="B94" s="1" t="n">
-        <v>45952</v>
+      <c r="B94" s="2" t="n">
+        <v>45933</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G94" s="2">
+        <v>7</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G94" s="3">
         <f>E94*F94</f>
         <v/>
       </c>
@@ -3398,12 +3289,12 @@
       <c r="A95" t="n">
         <v>1094</v>
       </c>
-      <c r="B95" s="1" t="n">
-        <v>45935</v>
+      <c r="B95" s="2" t="n">
+        <v>45936</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3412,12 +3303,12 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G95" s="3">
         <f>E95*F95</f>
         <v/>
       </c>
@@ -3426,12 +3317,12 @@
       <c r="A96" t="n">
         <v>1095</v>
       </c>
-      <c r="B96" s="1" t="n">
-        <v>45954</v>
+      <c r="B96" s="2" t="n">
+        <v>45950</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3440,12 +3331,12 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
-      </c>
-      <c r="F96" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="G96" s="2">
+      <c r="G96" s="3">
         <f>E96*F96</f>
         <v/>
       </c>
@@ -3454,26 +3345,26 @@
       <c r="A97" t="n">
         <v>1096</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G97" s="2">
+        <v>10</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G97" s="3">
         <f>E97*F97</f>
         <v/>
       </c>
@@ -3482,26 +3373,26 @@
       <c r="A98" t="n">
         <v>1097</v>
       </c>
-      <c r="B98" s="1" t="n">
-        <v>45937</v>
+      <c r="B98" s="2" t="n">
+        <v>45934</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G98" s="2">
+        <v>6</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G98" s="3">
         <f>E98*F98</f>
         <v/>
       </c>
@@ -3510,26 +3401,26 @@
       <c r="A99" t="n">
         <v>1098</v>
       </c>
-      <c r="B99" s="1" t="n">
-        <v>45947</v>
+      <c r="B99" s="2" t="n">
+        <v>45935</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G99" s="2">
+        <v>10</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G99" s="3">
         <f>E99*F99</f>
         <v/>
       </c>
@@ -3538,8 +3429,8 @@
       <c r="A100" t="n">
         <v>1099</v>
       </c>
-      <c r="B100" s="1" t="n">
-        <v>45933</v>
+      <c r="B100" s="2" t="n">
+        <v>45937</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3548,16 +3439,16 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>8</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G100" s="2">
+        <v>11</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G100" s="3">
         <f>E100*F100</f>
         <v/>
       </c>
@@ -3566,26 +3457,26 @@
       <c r="A101" t="n">
         <v>1100</v>
       </c>
-      <c r="B101" s="1" t="n">
-        <v>45932</v>
+      <c r="B101" s="2" t="n">
+        <v>45951</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G101" s="2">
+        <v>12</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G101" s="3">
         <f>E101*F101</f>
         <v/>
       </c>
@@ -3594,26 +3485,26 @@
       <c r="A102" t="n">
         <v>1101</v>
       </c>
-      <c r="B102" s="1" t="n">
-        <v>45982</v>
+      <c r="B102" s="2" t="n">
+        <v>45970</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G102" s="2">
+        <v>9</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G102" s="3">
         <f>E102*F102</f>
         <v/>
       </c>
@@ -3622,26 +3513,26 @@
       <c r="A103" t="n">
         <v>1102</v>
       </c>
-      <c r="B103" s="1" t="n">
-        <v>45979</v>
+      <c r="B103" s="2" t="n">
+        <v>45975</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>8</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G103" s="2">
+        <v>12</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G103" s="3">
         <f>E103*F103</f>
         <v/>
       </c>
@@ -3650,12 +3541,12 @@
       <c r="A104" t="n">
         <v>1103</v>
       </c>
-      <c r="B104" s="1" t="n">
-        <v>45965</v>
+      <c r="B104" s="2" t="n">
+        <v>45972</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3664,12 +3555,12 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
-      </c>
-      <c r="F104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="G104" s="2">
+      <c r="G104" s="3">
         <f>E104*F104</f>
         <v/>
       </c>
@@ -3678,26 +3569,26 @@
       <c r="A105" t="n">
         <v>1104</v>
       </c>
-      <c r="B105" s="1" t="n">
-        <v>45988</v>
+      <c r="B105" s="2" t="n">
+        <v>45967</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>11</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G105" s="2">
+        <v>6</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G105" s="3">
         <f>E105*F105</f>
         <v/>
       </c>
@@ -3706,26 +3597,26 @@
       <c r="A106" t="n">
         <v>1105</v>
       </c>
-      <c r="B106" s="1" t="n">
-        <v>45975</v>
+      <c r="B106" s="2" t="n">
+        <v>45979</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G106" s="2">
+        <v>8</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G106" s="3">
         <f>E106*F106</f>
         <v/>
       </c>
@@ -3734,8 +3625,8 @@
       <c r="A107" t="n">
         <v>1106</v>
       </c>
-      <c r="B107" s="1" t="n">
-        <v>45973</v>
+      <c r="B107" s="2" t="n">
+        <v>45984</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3748,12 +3639,12 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
-      </c>
-      <c r="F107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="G107" s="2">
+      <c r="G107" s="3">
         <f>E107*F107</f>
         <v/>
       </c>
@@ -3762,26 +3653,26 @@
       <c r="A108" t="n">
         <v>1107</v>
       </c>
-      <c r="B108" s="1" t="n">
-        <v>45983</v>
+      <c r="B108" s="2" t="n">
+        <v>45988</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G108" s="2">
+        <v>2</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G108" s="3">
         <f>E108*F108</f>
         <v/>
       </c>
@@ -3790,12 +3681,12 @@
       <c r="A109" t="n">
         <v>1108</v>
       </c>
-      <c r="B109" s="1" t="n">
-        <v>45973</v>
+      <c r="B109" s="2" t="n">
+        <v>45966</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3804,12 +3695,12 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
-      </c>
-      <c r="F109" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F109" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="G109" s="2">
+      <c r="G109" s="3">
         <f>E109*F109</f>
         <v/>
       </c>
@@ -3818,12 +3709,12 @@
       <c r="A110" t="n">
         <v>1109</v>
       </c>
-      <c r="B110" s="1" t="n">
-        <v>45969</v>
+      <c r="B110" s="2" t="n">
+        <v>45971</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3832,12 +3723,12 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
-      </c>
-      <c r="F110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="G110" s="2">
+      <c r="G110" s="3">
         <f>E110*F110</f>
         <v/>
       </c>
@@ -3846,26 +3737,26 @@
       <c r="A111" t="n">
         <v>1110</v>
       </c>
-      <c r="B111" s="1" t="n">
-        <v>45962</v>
+      <c r="B111" s="2" t="n">
+        <v>45968</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Laptop Stand</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>7</v>
       </c>
-      <c r="F111" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G111" s="2">
+      <c r="F111" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G111" s="3">
         <f>E111*F111</f>
         <v/>
       </c>
@@ -3874,12 +3765,12 @@
       <c r="A112" t="n">
         <v>1111</v>
       </c>
-      <c r="B112" s="1" t="n">
-        <v>46017</v>
+      <c r="B112" s="2" t="n">
+        <v>46003</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3888,12 +3779,12 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5</v>
-      </c>
-      <c r="F112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="G112" s="2">
+      <c r="G112" s="3">
         <f>E112*F112</f>
         <v/>
       </c>
@@ -3902,26 +3793,26 @@
       <c r="A113" t="n">
         <v>1112</v>
       </c>
-      <c r="B113" s="1" t="n">
-        <v>45997</v>
+      <c r="B113" s="2" t="n">
+        <v>45999</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Headset</t>
+          <t>Webcam</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G113" s="2">
+        <v>4</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G113" s="3">
         <f>E113*F113</f>
         <v/>
       </c>
@@ -3930,8 +3821,8 @@
       <c r="A114" t="n">
         <v>1113</v>
       </c>
-      <c r="B114" s="1" t="n">
-        <v>46019</v>
+      <c r="B114" s="2" t="n">
+        <v>45992</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -3940,16 +3831,16 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>9</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G114" s="2">
+        <v>8</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G114" s="3">
         <f>E114*F114</f>
         <v/>
       </c>
@@ -3958,26 +3849,26 @@
       <c r="A115" t="n">
         <v>1114</v>
       </c>
-      <c r="B115" s="1" t="n">
-        <v>45998</v>
+      <c r="B115" s="2" t="n">
+        <v>46017</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>USB Hub</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>7</v>
       </c>
-      <c r="F115" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="G115" s="2">
+      <c r="F115" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G115" s="3">
         <f>E115*F115</f>
         <v/>
       </c>
@@ -3986,26 +3877,26 @@
       <c r="A116" t="n">
         <v>1115</v>
       </c>
-      <c r="B116" s="1" t="n">
-        <v>46018</v>
+      <c r="B116" s="2" t="n">
+        <v>46000</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>5</v>
       </c>
-      <c r="F116" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G116" s="2">
+      <c r="F116" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G116" s="3">
         <f>E116*F116</f>
         <v/>
       </c>
@@ -4014,26 +3905,26 @@
       <c r="A117" t="n">
         <v>1116</v>
       </c>
-      <c r="B117" s="1" t="n">
-        <v>46013</v>
+      <c r="B117" s="2" t="n">
+        <v>46004</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wireless Mouse</t>
+          <t>Headset</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>8</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="G117" s="2">
+        <v>3</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G117" s="3">
         <f>E117*F117</f>
         <v/>
       </c>
@@ -4042,26 +3933,26 @@
       <c r="A118" t="n">
         <v>1117</v>
       </c>
-      <c r="B118" s="1" t="n">
-        <v>46000</v>
+      <c r="B118" s="2" t="n">
+        <v>45998</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G118" s="2">
+        <v>5</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G118" s="3">
         <f>E118*F118</f>
         <v/>
       </c>
@@ -4070,26 +3961,26 @@
       <c r="A119" t="n">
         <v>1118</v>
       </c>
-      <c r="B119" s="1" t="n">
-        <v>46012</v>
+      <c r="B119" s="2" t="n">
+        <v>46018</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Webcam</t>
+          <t>Keyboard</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G119" s="2">
+        <v>6</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G119" s="3">
         <f>E119*F119</f>
         <v/>
       </c>
@@ -4098,8 +3989,8 @@
       <c r="A120" t="n">
         <v>1119</v>
       </c>
-      <c r="B120" s="1" t="n">
-        <v>45992</v>
+      <c r="B120" s="2" t="n">
+        <v>46013</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -4108,16 +3999,16 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Laptop Stand</t>
+          <t>Wireless Mouse</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="G120" s="3">
         <f>E120*F120</f>
         <v/>
       </c>
@@ -4126,8 +4017,8 @@
       <c r="A121" t="n">
         <v>1120</v>
       </c>
-      <c r="B121" s="1" t="n">
-        <v>46010</v>
+      <c r="B121" s="2" t="n">
+        <v>46000</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -4136,16 +4027,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Keyboard</t>
+          <t>USB Hub</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G121" s="2">
+        <v>7</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G121" s="3">
         <f>E121*F121</f>
         <v/>
       </c>
@@ -4178,103 +4069,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ASHISH KUMAR — EXCEL SALES DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Sample portfolio project | Fictional data for demonstration</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>TOTAL ORDERS</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>TOTAL UNITS</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>AVG ORDER VALUE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <f>SUM('Sales Data'!G2:G121)</f>
         <v/>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <f>COUNTA('Sales Data'!A2:A121)</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>SUM('Sales Data'!E2:E121)</f>
         <v/>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <f>AVERAGE('Sales Data'!G2:G121)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>MONTHLY SALES</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>REGION SALES</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>PRODUCT SALES</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
@@ -4286,7 +4179,7 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,1,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,1,1),1))</f>
         <v/>
       </c>
@@ -4295,7 +4188,7 @@
           <t>North</t>
         </is>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <f>SUMIF('Sales Data'!$C$2:$C$121,D11,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4304,7 +4197,7 @@
           <t>Laptop Stand</t>
         </is>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G11,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4315,7 +4208,7 @@
           <t>Feb</t>
         </is>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,2,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,2,1),1))</f>
         <v/>
       </c>
@@ -4324,7 +4217,7 @@
           <t>South</t>
         </is>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <f>SUMIF('Sales Data'!$C$2:$C$121,D12,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4333,7 +4226,7 @@
           <t>Wireless Mouse</t>
         </is>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G12,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4344,7 +4237,7 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,3,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,3,1),1))</f>
         <v/>
       </c>
@@ -4353,7 +4246,7 @@
           <t>East</t>
         </is>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="3">
         <f>SUMIF('Sales Data'!$C$2:$C$121,D13,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4362,7 +4255,7 @@
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G13,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4373,7 +4266,7 @@
           <t>Apr</t>
         </is>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,4,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,4,1),1))</f>
         <v/>
       </c>
@@ -4382,7 +4275,7 @@
           <t>West</t>
         </is>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <f>SUMIF('Sales Data'!$C$2:$C$121,D14,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4391,7 +4284,7 @@
           <t>USB Hub</t>
         </is>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G14,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4402,7 +4295,7 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,5,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,5,1),1))</f>
         <v/>
       </c>
@@ -4411,7 +4304,7 @@
           <t>Webcam</t>
         </is>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G15,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4422,7 +4315,7 @@
           <t>Jun</t>
         </is>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,6,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,6,1),1))</f>
         <v/>
       </c>
@@ -4431,7 +4324,7 @@
           <t>Headset</t>
         </is>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <f>SUMIF('Sales Data'!$D$2:$D$121,G16,'Sales Data'!$G$2:$G$121)</f>
         <v/>
       </c>
@@ -4442,7 +4335,7 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,7,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,7,1),1))</f>
         <v/>
       </c>
@@ -4453,7 +4346,7 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,8,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,8,1),1))</f>
         <v/>
       </c>
@@ -4464,7 +4357,7 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,9,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,9,1),1))</f>
         <v/>
       </c>
@@ -4475,7 +4368,7 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,10,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,10,1),1))</f>
         <v/>
       </c>
@@ -4486,7 +4379,7 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,11,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,11,1),1))</f>
         <v/>
       </c>
@@ -4497,7 +4390,7 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <f>SUMIFS('Sales Data'!$G$2:$G$121,'Sales Data'!$B$2:$B$121,"&gt;="&amp;DATE(2025,12,1),'Sales Data'!$B$2:$B$121,"&lt;"&amp;EDATE(DATE(2025,12,1),1))</f>
         <v/>
       </c>
@@ -4525,7 +4418,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>PORTFOLIO PROJECT NOTE</t>
         </is>
@@ -4541,7 +4434,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Purpose: Portfolio demonstration of Excel data management and dashboard skills.</t>
+          <t>Purpose: Demonstration of Excel dashboard and analysis skills.</t>
         </is>
       </c>
     </row>
@@ -4555,14 +4448,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skills demonstrated: formulas, SUMIFS/SUMIF, tables, formatting, KPIs, charts and data organization.</t>
+          <t>Skills: formulas, SUMIFS/SUMIF, tables, KPIs, formatting and charts.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Suggested portfolio label: “Sample Project — Excel Sales Dashboard”.</t>
+          <t>Suggested portfolio label: Sample Project — Excel Sales Dashboard</t>
         </is>
       </c>
     </row>
